--- a/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E309A053-CC90-468C-8698-EB92CEE9F53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F824E45F-3A35-4DD9-80BC-CE655A195102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -540,7 +540,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="194">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1109,6 +1109,29 @@
   </si>
   <si>
     <t>累计经验提高能力等级</t>
+  </si>
+  <si>
+    <t>三选一道具</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得一次三选一</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能道具2</t>
+  </si>
+  <si>
+    <t>技能道具3</t>
+  </si>
+  <si>
+    <t>技能道具4</t>
+  </si>
+  <si>
+    <t>技能道具5</t>
+  </si>
+  <si>
+    <t>技能道具6</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1682,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BF72"/>
+  <dimension ref="A1:BF79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -14386,6 +14409,1238 @@
         <v>0</v>
       </c>
     </row>
+    <row r="73" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
+        <v>48200001</v>
+      </c>
+      <c r="B73" s="1">
+        <v>482</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G73" s="12">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J73" s="4">
+        <v>43400002</v>
+      </c>
+      <c r="K73" s="12">
+        <v>5</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M73" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N73" s="12">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>0</v>
+      </c>
+      <c r="R73" s="12">
+        <v>0</v>
+      </c>
+      <c r="S73" s="12">
+        <v>0</v>
+      </c>
+      <c r="T73" s="12">
+        <v>3</v>
+      </c>
+      <c r="U73" s="12">
+        <v>3</v>
+      </c>
+      <c r="V73" s="12">
+        <v>0</v>
+      </c>
+      <c r="W73" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="X73" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y73" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR73" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS73" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW73" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX73" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY73" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ73" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA73" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB73" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC73" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD73" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE73" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A74" s="1">
+        <v>48300001</v>
+      </c>
+      <c r="B74" s="1">
+        <v>483</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J74" s="4">
+        <v>43400002</v>
+      </c>
+      <c r="K74" s="12">
+        <v>5</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M74" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N74" s="12">
+        <v>0</v>
+      </c>
+      <c r="O74" s="12">
+        <v>0</v>
+      </c>
+      <c r="P74" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
+      <c r="R74" s="12">
+        <v>0</v>
+      </c>
+      <c r="S74" s="12">
+        <v>0</v>
+      </c>
+      <c r="T74" s="12">
+        <v>3</v>
+      </c>
+      <c r="U74" s="12">
+        <v>3</v>
+      </c>
+      <c r="V74" s="12">
+        <v>0</v>
+      </c>
+      <c r="W74" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="X74" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y74" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR74" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS74" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW74" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ74" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA74" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB74" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC74" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD74" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE74" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A75" s="1">
+        <v>48300002</v>
+      </c>
+      <c r="B75" s="1">
+        <v>483</v>
+      </c>
+      <c r="C75" s="1">
+        <v>2</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12">
+        <v>0</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J75" s="4">
+        <v>43400002</v>
+      </c>
+      <c r="K75" s="12">
+        <v>5</v>
+      </c>
+      <c r="L75" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M75" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N75" s="12">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12">
+        <v>0</v>
+      </c>
+      <c r="P75" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>0</v>
+      </c>
+      <c r="R75" s="12">
+        <v>0</v>
+      </c>
+      <c r="S75" s="12">
+        <v>0</v>
+      </c>
+      <c r="T75" s="12">
+        <v>3</v>
+      </c>
+      <c r="U75" s="12">
+        <v>3</v>
+      </c>
+      <c r="V75" s="12">
+        <v>0</v>
+      </c>
+      <c r="W75" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="X75" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y75" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR75" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS75" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW75" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX75" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY75" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ75" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA75" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB75" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC75" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD75" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE75" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A76" s="1">
+        <v>48300003</v>
+      </c>
+      <c r="B76" s="1">
+        <v>483</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G76" s="12">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12">
+        <v>0</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J76" s="4">
+        <v>43400002</v>
+      </c>
+      <c r="K76" s="12">
+        <v>5</v>
+      </c>
+      <c r="L76" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M76" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N76" s="12">
+        <v>0</v>
+      </c>
+      <c r="O76" s="12">
+        <v>0</v>
+      </c>
+      <c r="P76" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
+      <c r="R76" s="12">
+        <v>0</v>
+      </c>
+      <c r="S76" s="12">
+        <v>0</v>
+      </c>
+      <c r="T76" s="12">
+        <v>3</v>
+      </c>
+      <c r="U76" s="12">
+        <v>3</v>
+      </c>
+      <c r="V76" s="12">
+        <v>0</v>
+      </c>
+      <c r="W76" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="X76" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y76" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR76" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS76" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW76" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX76" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY76" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ76" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA76" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB76" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC76" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD76" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE76" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A77" s="1">
+        <v>48300004</v>
+      </c>
+      <c r="B77" s="1">
+        <v>483</v>
+      </c>
+      <c r="C77" s="1">
+        <v>4</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G77" s="12">
+        <v>0</v>
+      </c>
+      <c r="H77" s="12">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J77" s="4">
+        <v>43400002</v>
+      </c>
+      <c r="K77" s="12">
+        <v>5</v>
+      </c>
+      <c r="L77" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M77" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N77" s="12">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
+      <c r="R77" s="12">
+        <v>0</v>
+      </c>
+      <c r="S77" s="12">
+        <v>0</v>
+      </c>
+      <c r="T77" s="12">
+        <v>3</v>
+      </c>
+      <c r="U77" s="12">
+        <v>3</v>
+      </c>
+      <c r="V77" s="12">
+        <v>0</v>
+      </c>
+      <c r="W77" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="X77" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y77" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR77" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS77" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW77" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX77" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY77" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ77" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA77" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB77" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC77" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD77" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE77" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A78" s="1">
+        <v>48300005</v>
+      </c>
+      <c r="B78" s="1">
+        <v>483</v>
+      </c>
+      <c r="C78" s="1">
+        <v>5</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12">
+        <v>0</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J78" s="4">
+        <v>43400002</v>
+      </c>
+      <c r="K78" s="12">
+        <v>5</v>
+      </c>
+      <c r="L78" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M78" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N78" s="12">
+        <v>0</v>
+      </c>
+      <c r="O78" s="12">
+        <v>0</v>
+      </c>
+      <c r="P78" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="12">
+        <v>0</v>
+      </c>
+      <c r="R78" s="12">
+        <v>0</v>
+      </c>
+      <c r="S78" s="12">
+        <v>0</v>
+      </c>
+      <c r="T78" s="12">
+        <v>3</v>
+      </c>
+      <c r="U78" s="12">
+        <v>3</v>
+      </c>
+      <c r="V78" s="12">
+        <v>0</v>
+      </c>
+      <c r="W78" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="X78" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y78" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR78" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS78" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW78" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX78" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY78" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ78" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA78" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB78" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC78" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD78" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE78" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:58" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
+        <v>48300006</v>
+      </c>
+      <c r="B79" s="1">
+        <v>483</v>
+      </c>
+      <c r="C79" s="1">
+        <v>6</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G79" s="12">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J79" s="4">
+        <v>43400002</v>
+      </c>
+      <c r="K79" s="12">
+        <v>5</v>
+      </c>
+      <c r="L79" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M79" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N79" s="12">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12">
+        <v>0</v>
+      </c>
+      <c r="P79" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="12">
+        <v>0</v>
+      </c>
+      <c r="R79" s="12">
+        <v>0</v>
+      </c>
+      <c r="S79" s="12">
+        <v>0</v>
+      </c>
+      <c r="T79" s="12">
+        <v>3</v>
+      </c>
+      <c r="U79" s="12">
+        <v>3</v>
+      </c>
+      <c r="V79" s="12">
+        <v>0</v>
+      </c>
+      <c r="W79" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="X79" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y79" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="12">
+        <v>2</v>
+      </c>
+      <c r="AE79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AL79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR79" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS79" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW79" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX79" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY79" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ79" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA79" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB79" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC79" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD79" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE79" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF79" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:BE63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="11" type="noConversion"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F824E45F-3A35-4DD9-80BC-CE655A195102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933182A1-F67A-41BC-B7C3-3221F9462EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -540,7 +540,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="195">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1132,6 +1132,10 @@
   </si>
   <si>
     <t>技能道具6</t>
+  </si>
+  <si>
+    <t>items_0</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -14435,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J73" s="4">
-        <v>43400002</v>
+        <v>48200001</v>
       </c>
       <c r="K73" s="12">
         <v>5</v>
@@ -14611,10 +14615,10 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J74" s="4">
-        <v>43400002</v>
+        <v>48300001</v>
       </c>
       <c r="K74" s="12">
         <v>5</v>
@@ -14787,10 +14791,10 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J75" s="4">
-        <v>43400002</v>
+        <v>48300002</v>
       </c>
       <c r="K75" s="12">
         <v>5</v>
@@ -14963,10 +14967,10 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J76" s="4">
-        <v>43400002</v>
+        <v>48300003</v>
       </c>
       <c r="K76" s="12">
         <v>5</v>
@@ -15139,10 +15143,10 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J77" s="4">
-        <v>43400002</v>
+        <v>48300004</v>
       </c>
       <c r="K77" s="12">
         <v>5</v>
@@ -15315,10 +15319,10 @@
         <v>0</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J78" s="4">
-        <v>43400002</v>
+        <v>48300005</v>
       </c>
       <c r="K78" s="12">
         <v>5</v>
@@ -15491,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="J79" s="4">
-        <v>43400002</v>
+        <v>48300006</v>
       </c>
       <c r="K79" s="12">
         <v>5</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933182A1-F67A-41BC-B7C3-3221F9462EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27F662C-0BBB-4017-ABE0-5C01A8CDF0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_items_v8" sheetId="16" r:id="rId1"/>
@@ -1134,7 +1134,7 @@
     <t>技能道具6</t>
   </si>
   <si>
-    <t>items_0</t>
+    <t>items</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27F662C-0BBB-4017-ABE0-5C01A8CDF0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18282645-7DC2-4691-A99A-DE806F821AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -540,7 +540,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="193">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -902,9 +902,6 @@
     <t>人偶版出售后得到货币的ID</t>
   </si>
   <si>
-    <t>items_atlas_0</t>
-  </si>
-  <si>
     <t>common_ui_atlas_0</t>
   </si>
   <si>
@@ -921,9 +918,6 @@
   </si>
   <si>
     <t>wz_bg_03</t>
-  </si>
-  <si>
-    <t>items_1_atlas_0</t>
   </si>
   <si>
     <t>资源</t>
@@ -1134,7 +1128,7 @@
     <t>技能道具6</t>
   </si>
   <si>
-    <t>items</t>
+    <t>items_atlas0</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2090,7 +2084,7 @@
         <v>10</v>
       </c>
       <c r="BF2" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:58" x14ac:dyDescent="0.15">
@@ -2266,7 +2260,7 @@
         <v>72</v>
       </c>
       <c r="BF3" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:58" x14ac:dyDescent="0.15">
@@ -2442,7 +2436,7 @@
         <v>98</v>
       </c>
       <c r="BF4" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:58" x14ac:dyDescent="0.15">
@@ -2456,13 +2450,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -2470,23 +2464,23 @@
       <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -2513,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y5" s="1">
         <v>0</v>
@@ -2579,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT5" s="1">
         <v>0</v>
@@ -2600,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="AZ5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA5" s="1">
         <v>0</v>
@@ -2612,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="BD5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE5" s="1">
         <v>0</v>
@@ -2632,13 +2626,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2646,23 +2640,23 @@
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -2689,10 +2683,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -2755,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="AS6" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT6" s="1">
         <v>0</v>
@@ -2776,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="AZ6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA6" s="1">
         <v>0</v>
@@ -2788,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="BD6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE6" s="1">
         <v>0</v>
@@ -2808,13 +2802,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2822,23 +2816,23 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -2865,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -2931,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT7" s="1">
         <v>0</v>
@@ -2952,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA7" s="1">
         <v>0</v>
@@ -2964,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE7" s="1">
         <v>0</v>
@@ -2984,13 +2978,13 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2998,23 +2992,23 @@
       <c r="H8" s="1">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -3041,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
@@ -3107,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="AS8" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT8" s="1">
         <v>0</v>
@@ -3128,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="AZ8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA8" s="1">
         <v>0</v>
@@ -3140,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="BD8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE8" s="1">
         <v>0</v>
@@ -3160,13 +3154,13 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -3174,23 +3168,23 @@
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -3217,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
@@ -3283,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -3304,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="AZ9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA9" s="1">
         <v>0</v>
@@ -3316,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="BD9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE9" s="1">
         <v>0</v>
@@ -3336,13 +3330,13 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -3350,23 +3344,23 @@
       <c r="H10" s="1">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -3393,10 +3387,10 @@
         <v>0</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
@@ -3459,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="AS10" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT10" s="1">
         <v>0</v>
@@ -3480,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="AZ10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA10" s="1">
         <v>0</v>
@@ -3492,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="BD10" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE10" s="1">
         <v>0</v>
@@ -3512,13 +3506,13 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -3526,23 +3520,23 @@
       <c r="H11" s="1">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -3569,10 +3563,10 @@
         <v>0</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -3635,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="AS11" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT11" s="1">
         <v>0</v>
@@ -3656,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA11" s="1">
         <v>0</v>
@@ -3668,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="BD11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE11" s="1">
         <v>0</v>
@@ -3688,13 +3682,13 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -3703,22 +3697,22 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -3745,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -3811,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="AS12" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT12" s="1">
         <v>0</v>
@@ -3832,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA12" s="1">
         <v>0</v>
@@ -3844,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="BD12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE12" s="1">
         <v>0</v>
@@ -3864,13 +3858,13 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -3879,22 +3873,22 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -3921,10 +3915,10 @@
         <v>0</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
@@ -3987,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="AS13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT13" s="1">
         <v>0</v>
@@ -4008,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="AZ13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA13" s="1">
         <v>0</v>
@@ -4020,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="BD13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE13" s="1">
         <v>0</v>
@@ -4040,13 +4034,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -4055,22 +4049,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -4097,10 +4091,10 @@
         <v>0</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y14" s="1">
         <v>0</v>
@@ -4163,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="AS14" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT14" s="1">
         <v>0</v>
@@ -4184,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="AZ14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA14" s="1">
         <v>0</v>
@@ -4196,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="BD14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE14" s="1">
         <v>0</v>
@@ -4216,13 +4210,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -4231,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -4273,10 +4267,10 @@
         <v>0</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y15" s="1">
         <v>0</v>
@@ -4339,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AS15" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT15" s="1">
         <v>0</v>
@@ -4360,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="AZ15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA15" s="1">
         <v>0</v>
@@ -4372,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="BD15" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE15" s="1">
         <v>0</v>
@@ -4392,13 +4386,13 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -4407,22 +4401,22 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -4449,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y16" s="1">
         <v>0</v>
@@ -4515,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="AS16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT16" s="1">
         <v>0</v>
@@ -4536,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA16" s="1">
         <v>0</v>
@@ -4548,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="BD16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE16" s="1">
         <v>0</v>
@@ -4568,13 +4562,13 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -4583,22 +4577,22 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -4625,10 +4619,10 @@
         <v>0</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y17" s="1">
         <v>0</v>
@@ -4691,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="AS17" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT17" s="1">
         <v>0</v>
@@ -4712,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="AZ17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA17" s="1">
         <v>0</v>
@@ -4724,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="BD17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE17" s="1">
         <v>0</v>
@@ -4744,13 +4738,13 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -4759,22 +4753,22 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -4801,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
@@ -4867,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="AS18" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT18" s="1">
         <v>0</v>
@@ -4888,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="AZ18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA18" s="1">
         <v>0</v>
@@ -4900,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="BD18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE18" s="1">
         <v>0</v>
@@ -4920,13 +4914,13 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -4935,22 +4929,22 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -4977,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y19" s="1">
         <v>0</v>
@@ -5043,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="AS19" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT19" s="1">
         <v>0</v>
@@ -5064,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="AZ19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA19" s="1">
         <v>0</v>
@@ -5076,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="BD19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE19" s="1">
         <v>0</v>
@@ -5096,13 +5090,13 @@
         <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -5111,22 +5105,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -5153,10 +5147,10 @@
         <v>0</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y20" s="1">
         <v>0</v>
@@ -5219,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="AS20" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT20" s="1">
         <v>0</v>
@@ -5240,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="AZ20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA20" s="1">
         <v>0</v>
@@ -5252,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="BD20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE20" s="1">
         <v>0</v>
@@ -5272,13 +5266,13 @@
         <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -5287,22 +5281,22 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -5329,10 +5323,10 @@
         <v>0</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
@@ -5395,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="AS21" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT21" s="1">
         <v>0</v>
@@ -5416,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="AZ21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA21" s="1">
         <v>0</v>
@@ -5428,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="BD21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE21" s="1">
         <v>0</v>
@@ -5448,13 +5442,13 @@
         <v>19</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -5463,22 +5457,22 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -5505,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y22" s="1">
         <v>0</v>
@@ -5571,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="AS22" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT22" s="1">
         <v>0</v>
@@ -5592,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="AZ22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA22" s="1">
         <v>0</v>
@@ -5604,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="BD22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE22" s="1">
         <v>0</v>
@@ -5624,13 +5618,13 @@
         <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -5639,22 +5633,22 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -5681,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y23" s="1">
         <v>0</v>
@@ -5747,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AS23" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT23" s="1">
         <v>0</v>
@@ -5768,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="AZ23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA23" s="1">
         <v>0</v>
@@ -5780,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="BD23" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE23" s="1">
         <v>0</v>
@@ -5800,13 +5794,13 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -5815,22 +5809,22 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -5857,10 +5851,10 @@
         <v>0</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -5923,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="AS24" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT24" s="1">
         <v>0</v>
@@ -5944,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="AZ24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA24" s="1">
         <v>0</v>
@@ -5956,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="BD24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE24" s="1">
         <v>0</v>
@@ -5976,13 +5970,13 @@
         <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -5991,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -6033,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -6099,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="AS25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT25" s="1">
         <v>0</v>
@@ -6120,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="AZ25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA25" s="1">
         <v>0</v>
@@ -6132,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="BD25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE25" s="1">
         <v>0</v>
@@ -6152,13 +6146,13 @@
         <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -6167,22 +6161,22 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -6209,10 +6203,10 @@
         <v>0</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y26" s="1">
         <v>0</v>
@@ -6275,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="AS26" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT26" s="1">
         <v>0</v>
@@ -6296,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="AZ26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA26" s="1">
         <v>0</v>
@@ -6308,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="BD26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE26" s="1">
         <v>0</v>
@@ -6328,13 +6322,13 @@
         <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -6343,22 +6337,22 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -6385,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y27" s="1">
         <v>0</v>
@@ -6451,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="AS27" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT27" s="1">
         <v>0</v>
@@ -6472,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="AZ27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA27" s="1">
         <v>0</v>
@@ -6484,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="BD27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE27" s="1">
         <v>0</v>
@@ -6504,13 +6498,13 @@
         <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -6519,22 +6513,22 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -6561,10 +6555,10 @@
         <v>0</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y28" s="1">
         <v>0</v>
@@ -6627,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="AS28" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT28" s="1">
         <v>0</v>
@@ -6648,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="AZ28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA28" s="1">
         <v>0</v>
@@ -6660,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="BD28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE28" s="1">
         <v>0</v>
@@ -6680,13 +6674,13 @@
         <v>26</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -6695,22 +6689,22 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -6737,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y29" s="1">
         <v>0</v>
@@ -6803,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AS29" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT29" s="1">
         <v>0</v>
@@ -6824,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="AZ29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA29" s="1">
         <v>0</v>
@@ -6836,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="BD29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE29" s="1">
         <v>0</v>
@@ -6856,13 +6850,13 @@
         <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -6871,22 +6865,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -6913,10 +6907,10 @@
         <v>0</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y30" s="1">
         <v>0</v>
@@ -6979,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT30" s="1">
         <v>0</v>
@@ -7000,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="AZ30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA30" s="1">
         <v>0</v>
@@ -7012,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="BD30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE30" s="1">
         <v>0</v>
@@ -7032,13 +7026,13 @@
         <v>28</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -7047,22 +7041,22 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -7089,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y31" s="1">
         <v>0</v>
@@ -7155,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AS31" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT31" s="1">
         <v>0</v>
@@ -7176,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="AZ31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA31" s="1">
         <v>0</v>
@@ -7188,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="BD31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE31" s="1">
         <v>0</v>
@@ -7208,13 +7202,13 @@
         <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -7223,22 +7217,22 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -7265,10 +7259,10 @@
         <v>0</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y32" s="1">
         <v>0</v>
@@ -7331,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="AS32" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT32" s="1">
         <v>0</v>
@@ -7352,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="AZ32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA32" s="1">
         <v>0</v>
@@ -7364,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="BD32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE32" s="1">
         <v>0</v>
@@ -7384,13 +7378,13 @@
         <v>30</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -7399,22 +7393,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -7441,10 +7435,10 @@
         <v>0</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y33" s="1">
         <v>0</v>
@@ -7507,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="AS33" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT33" s="1">
         <v>0</v>
@@ -7528,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="AZ33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA33" s="1">
         <v>0</v>
@@ -7540,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="BD33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE33" s="1">
         <v>0</v>
@@ -7560,13 +7554,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -7575,22 +7569,22 @@
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -7617,10 +7611,10 @@
         <v>0</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
@@ -7683,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="AS34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT34" s="1">
         <v>0</v>
@@ -7704,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="AZ34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA34" s="1">
         <v>0</v>
@@ -7716,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="BD34" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE34" s="1">
         <v>0</v>
@@ -7736,13 +7730,13 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -7751,22 +7745,22 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35" s="1">
         <v>0</v>
@@ -7793,10 +7787,10 @@
         <v>0</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y35" s="1">
         <v>0</v>
@@ -7859,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="AS35" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT35" s="1">
         <v>0</v>
@@ -7880,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="AZ35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA35" s="1">
         <v>0</v>
@@ -7892,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="BD35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE35" s="1">
         <v>0</v>
@@ -7912,13 +7906,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -7927,22 +7921,22 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -7969,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y36" s="1">
         <v>0</v>
@@ -8035,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT36" s="1">
         <v>0</v>
@@ -8056,7 +8050,7 @@
         <v>0</v>
       </c>
       <c r="AZ36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA36" s="1">
         <v>0</v>
@@ -8068,7 +8062,7 @@
         <v>0</v>
       </c>
       <c r="BD36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE36" s="1">
         <v>0</v>
@@ -8088,13 +8082,13 @@
         <v>4</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -8103,22 +8097,22 @@
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -8145,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y37" s="1">
         <v>0</v>
@@ -8211,7 +8205,7 @@
         <v>0</v>
       </c>
       <c r="AS37" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT37" s="1">
         <v>0</v>
@@ -8232,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="AZ37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA37" s="1">
         <v>0</v>
@@ -8244,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="BD37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE37" s="1">
         <v>0</v>
@@ -8264,13 +8258,13 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -8279,22 +8273,22 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O38" s="1">
         <v>0</v>
@@ -8321,10 +8315,10 @@
         <v>0</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y38" s="1">
         <v>0</v>
@@ -8387,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="AS38" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -8408,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="AZ38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA38" s="1">
         <v>0</v>
@@ -8420,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="BD38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE38" s="1">
         <v>0</v>
@@ -8440,13 +8434,13 @@
         <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -8455,22 +8449,22 @@
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -8497,10 +8491,10 @@
         <v>0</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y39" s="1">
         <v>0</v>
@@ -8563,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="AS39" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT39" s="1">
         <v>0</v>
@@ -8584,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="AZ39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA39" s="1">
         <v>0</v>
@@ -8596,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="BD39" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE39" s="1">
         <v>0</v>
@@ -8616,13 +8610,13 @@
         <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -8631,22 +8625,22 @@
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K40" s="1">
         <v>1</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
@@ -8673,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y40" s="1">
         <v>0</v>
@@ -8739,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="AS40" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT40" s="1">
         <v>0</v>
@@ -8760,7 +8754,7 @@
         <v>0</v>
       </c>
       <c r="AZ40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA40" s="1">
         <v>0</v>
@@ -8772,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="BD40" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE40" s="1">
         <v>0</v>
@@ -8792,13 +8786,13 @@
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -8807,22 +8801,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K41" s="1">
         <v>1</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -8849,10 +8843,10 @@
         <v>0</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y41" s="1">
         <v>0</v>
@@ -8915,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="AS41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT41" s="1">
         <v>0</v>
@@ -8936,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="AZ41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA41" s="1">
         <v>0</v>
@@ -8948,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="BD41" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE41" s="1">
         <v>0</v>
@@ -8968,13 +8962,13 @@
         <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -8983,22 +8977,22 @@
         <v>0</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K42" s="1">
         <v>1</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -9025,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y42" s="1">
         <v>0</v>
@@ -9091,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="AS42" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT42" s="1">
         <v>0</v>
@@ -9112,7 +9106,7 @@
         <v>0</v>
       </c>
       <c r="AZ42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA42" s="1">
         <v>0</v>
@@ -9124,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="BD42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE42" s="1">
         <v>0</v>
@@ -9144,13 +9138,13 @@
         <v>10</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -9159,22 +9153,22 @@
         <v>0</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O43" s="1">
         <v>0</v>
@@ -9201,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y43" s="1">
         <v>0</v>
@@ -9267,7 +9261,7 @@
         <v>0</v>
       </c>
       <c r="AS43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -9288,7 +9282,7 @@
         <v>0</v>
       </c>
       <c r="AZ43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA43" s="1">
         <v>0</v>
@@ -9300,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="BD43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE43" s="1">
         <v>0</v>
@@ -9320,13 +9314,13 @@
         <v>11</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -9335,22 +9329,22 @@
         <v>0</v>
       </c>
       <c r="I44" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K44" s="1">
         <v>1</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O44" s="1">
         <v>0</v>
@@ -9377,10 +9371,10 @@
         <v>0</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y44" s="1">
         <v>0</v>
@@ -9443,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="AS44" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT44" s="1">
         <v>0</v>
@@ -9464,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="AZ44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA44" s="1">
         <v>0</v>
@@ -9476,7 +9470,7 @@
         <v>0</v>
       </c>
       <c r="BD44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE44" s="1">
         <v>0</v>
@@ -9496,13 +9490,13 @@
         <v>12</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -9511,22 +9505,22 @@
         <v>0</v>
       </c>
       <c r="I45" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K45" s="1">
         <v>1</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -9553,10 +9547,10 @@
         <v>0</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y45" s="1">
         <v>0</v>
@@ -9619,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="AS45" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT45" s="1">
         <v>0</v>
@@ -9640,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="AZ45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA45" s="1">
         <v>0</v>
@@ -9652,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="BD45" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE45" s="1">
         <v>0</v>
@@ -9672,13 +9666,13 @@
         <v>13</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -9687,22 +9681,22 @@
         <v>0</v>
       </c>
       <c r="I46" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K46" s="1">
         <v>1</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -9729,10 +9723,10 @@
         <v>0</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
@@ -9795,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="AS46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT46" s="1">
         <v>0</v>
@@ -9816,7 +9810,7 @@
         <v>0</v>
       </c>
       <c r="AZ46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA46" s="1">
         <v>0</v>
@@ -9828,7 +9822,7 @@
         <v>0</v>
       </c>
       <c r="BD46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE46" s="1">
         <v>0</v>
@@ -9848,13 +9842,13 @@
         <v>14</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -9863,22 +9857,22 @@
         <v>0</v>
       </c>
       <c r="I47" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O47" s="1">
         <v>0</v>
@@ -9905,10 +9899,10 @@
         <v>0</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -9971,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="AS47" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT47" s="1">
         <v>0</v>
@@ -9992,7 +9986,7 @@
         <v>0</v>
       </c>
       <c r="AZ47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA47" s="1">
         <v>0</v>
@@ -10004,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BD47" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE47" s="1">
         <v>0</v>
@@ -10024,13 +10018,13 @@
         <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -10039,22 +10033,22 @@
         <v>0</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K48" s="1">
         <v>1</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -10081,10 +10075,10 @@
         <v>0</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y48" s="1">
         <v>0</v>
@@ -10147,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="AS48" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT48" s="1">
         <v>0</v>
@@ -10168,7 +10162,7 @@
         <v>0</v>
       </c>
       <c r="AZ48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA48" s="1">
         <v>0</v>
@@ -10180,7 +10174,7 @@
         <v>0</v>
       </c>
       <c r="BD48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE48" s="1">
         <v>0</v>
@@ -10200,13 +10194,13 @@
         <v>16</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -10215,22 +10209,22 @@
         <v>0</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K49" s="1">
         <v>1</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O49" s="1">
         <v>0</v>
@@ -10257,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y49" s="1">
         <v>0</v>
@@ -10323,7 +10317,7 @@
         <v>0</v>
       </c>
       <c r="AS49" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT49" s="1">
         <v>0</v>
@@ -10344,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="AZ49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA49" s="1">
         <v>0</v>
@@ -10356,7 +10350,7 @@
         <v>0</v>
       </c>
       <c r="BD49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE49" s="1">
         <v>0</v>
@@ -10376,13 +10370,13 @@
         <v>17</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -10391,22 +10385,22 @@
         <v>0</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K50" s="1">
         <v>1</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -10433,10 +10427,10 @@
         <v>0</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -10499,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="AS50" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT50" s="1">
         <v>0</v>
@@ -10520,7 +10514,7 @@
         <v>0</v>
       </c>
       <c r="AZ50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA50" s="1">
         <v>0</v>
@@ -10532,7 +10526,7 @@
         <v>0</v>
       </c>
       <c r="BD50" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE50" s="1">
         <v>0</v>
@@ -10552,13 +10546,13 @@
         <v>18</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -10567,22 +10561,22 @@
         <v>0</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K51" s="1">
         <v>1</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -10609,10 +10603,10 @@
         <v>0</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y51" s="1">
         <v>0</v>
@@ -10675,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="AS51" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT51" s="1">
         <v>0</v>
@@ -10696,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="AZ51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA51" s="1">
         <v>0</v>
@@ -10708,7 +10702,7 @@
         <v>0</v>
       </c>
       <c r="BD51" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE51" s="1">
         <v>0</v>
@@ -10728,13 +10722,13 @@
         <v>19</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -10743,22 +10737,22 @@
         <v>0</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K52" s="1">
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O52" s="1">
         <v>0</v>
@@ -10785,10 +10779,10 @@
         <v>0</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y52" s="1">
         <v>0</v>
@@ -10851,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AS52" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT52" s="1">
         <v>0</v>
@@ -10872,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="AZ52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA52" s="1">
         <v>0</v>
@@ -10884,7 +10878,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE52" s="1">
         <v>0</v>
@@ -10904,13 +10898,13 @@
         <v>20</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -10919,22 +10913,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K53" s="1">
         <v>1</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O53" s="1">
         <v>0</v>
@@ -10961,10 +10955,10 @@
         <v>0</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y53" s="1">
         <v>0</v>
@@ -11027,7 +11021,7 @@
         <v>0</v>
       </c>
       <c r="AS53" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT53" s="1">
         <v>0</v>
@@ -11048,7 +11042,7 @@
         <v>0</v>
       </c>
       <c r="AZ53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA53" s="1">
         <v>0</v>
@@ -11060,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="BD53" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE53" s="1">
         <v>0</v>
@@ -11080,13 +11074,13 @@
         <v>21</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -11095,22 +11089,22 @@
         <v>0</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K54" s="1">
         <v>1</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O54" s="1">
         <v>0</v>
@@ -11137,10 +11131,10 @@
         <v>0</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y54" s="1">
         <v>0</v>
@@ -11203,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AS54" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -11224,7 +11218,7 @@
         <v>0</v>
       </c>
       <c r="AZ54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA54" s="1">
         <v>0</v>
@@ -11236,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE54" s="1">
         <v>0</v>
@@ -11256,13 +11250,13 @@
         <v>22</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -11271,22 +11265,22 @@
         <v>0</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K55" s="1">
         <v>1</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O55" s="1">
         <v>0</v>
@@ -11313,10 +11307,10 @@
         <v>0</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y55" s="1">
         <v>0</v>
@@ -11379,7 +11373,7 @@
         <v>0</v>
       </c>
       <c r="AS55" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT55" s="1">
         <v>0</v>
@@ -11400,7 +11394,7 @@
         <v>0</v>
       </c>
       <c r="AZ55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA55" s="1">
         <v>0</v>
@@ -11412,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="BD55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE55" s="1">
         <v>0</v>
@@ -11432,13 +11426,13 @@
         <v>23</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -11447,22 +11441,22 @@
         <v>0</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K56" s="1">
         <v>1</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O56" s="1">
         <v>0</v>
@@ -11489,10 +11483,10 @@
         <v>0</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y56" s="1">
         <v>0</v>
@@ -11555,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="AS56" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT56" s="1">
         <v>0</v>
@@ -11576,7 +11570,7 @@
         <v>0</v>
       </c>
       <c r="AZ56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA56" s="1">
         <v>0</v>
@@ -11588,7 +11582,7 @@
         <v>0</v>
       </c>
       <c r="BD56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE56" s="1">
         <v>0</v>
@@ -11608,13 +11602,13 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -11623,22 +11617,22 @@
         <v>0</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K57" s="1">
         <v>1</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O57" s="1">
         <v>0</v>
@@ -11665,10 +11659,10 @@
         <v>0</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y57" s="1">
         <v>0</v>
@@ -11731,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="AS57" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT57" s="1">
         <v>0</v>
@@ -11752,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="AZ57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA57" s="1">
         <v>0</v>
@@ -11764,7 +11758,7 @@
         <v>0</v>
       </c>
       <c r="BD57" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE57" s="1">
         <v>0</v>
@@ -11784,13 +11778,13 @@
         <v>25</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -11799,22 +11793,22 @@
         <v>0</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K58" s="1">
         <v>1</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O58" s="1">
         <v>0</v>
@@ -11841,10 +11835,10 @@
         <v>0</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y58" s="1">
         <v>0</v>
@@ -11907,7 +11901,7 @@
         <v>0</v>
       </c>
       <c r="AS58" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT58" s="1">
         <v>0</v>
@@ -11928,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="AZ58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA58" s="1">
         <v>0</v>
@@ -11940,7 +11934,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE58" s="1">
         <v>0</v>
@@ -11960,13 +11954,13 @@
         <v>26</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -11975,22 +11969,22 @@
         <v>0</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K59" s="1">
         <v>1</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -12017,10 +12011,10 @@
         <v>0</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y59" s="1">
         <v>0</v>
@@ -12083,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="AS59" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT59" s="1">
         <v>0</v>
@@ -12104,7 +12098,7 @@
         <v>0</v>
       </c>
       <c r="AZ59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA59" s="1">
         <v>0</v>
@@ -12116,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="BD59" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE59" s="1">
         <v>0</v>
@@ -12136,13 +12130,13 @@
         <v>27</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -12151,22 +12145,22 @@
         <v>0</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K60" s="1">
         <v>1</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O60" s="1">
         <v>0</v>
@@ -12193,10 +12187,10 @@
         <v>0</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y60" s="1">
         <v>0</v>
@@ -12259,7 +12253,7 @@
         <v>0</v>
       </c>
       <c r="AS60" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT60" s="1">
         <v>0</v>
@@ -12280,7 +12274,7 @@
         <v>0</v>
       </c>
       <c r="AZ60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA60" s="1">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="BD60" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE60" s="1">
         <v>0</v>
@@ -12312,13 +12306,13 @@
         <v>28</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -12327,22 +12321,22 @@
         <v>0</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K61" s="1">
         <v>1</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -12369,10 +12363,10 @@
         <v>0</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y61" s="1">
         <v>0</v>
@@ -12435,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="AS61" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT61" s="1">
         <v>0</v>
@@ -12456,7 +12450,7 @@
         <v>0</v>
       </c>
       <c r="AZ61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA61" s="1">
         <v>0</v>
@@ -12468,7 +12462,7 @@
         <v>0</v>
       </c>
       <c r="BD61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE61" s="1">
         <v>0</v>
@@ -12488,13 +12482,13 @@
         <v>29</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -12503,22 +12497,22 @@
         <v>0</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K62" s="1">
         <v>1</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O62" s="1">
         <v>0</v>
@@ -12545,10 +12539,10 @@
         <v>0</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y62" s="1">
         <v>0</v>
@@ -12611,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="AS62" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT62" s="1">
         <v>0</v>
@@ -12632,7 +12626,7 @@
         <v>0</v>
       </c>
       <c r="AZ62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA62" s="1">
         <v>0</v>
@@ -12644,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="BD62" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE62" s="1">
         <v>0</v>
@@ -12664,13 +12658,13 @@
         <v>30</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -12679,22 +12673,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K63" s="1">
         <v>1</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O63" s="1">
         <v>0</v>
@@ -12721,10 +12715,10 @@
         <v>0</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y63" s="1">
         <v>0</v>
@@ -12787,7 +12781,7 @@
         <v>0</v>
       </c>
       <c r="AS63" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -12808,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA63" s="1">
         <v>0</v>
@@ -12820,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="BD63" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE63" s="1">
         <v>0</v>
@@ -12840,14 +12834,14 @@
         <v>2</v>
       </c>
       <c r="D64" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="E64" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>168</v>
-      </c>
       <c r="G64" s="12">
         <v>0</v>
       </c>
@@ -12855,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J64" s="4">
         <v>43400002</v>
@@ -12864,10 +12858,10 @@
         <v>5</v>
       </c>
       <c r="L64" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M64" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M64" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N64" s="12">
         <v>0</v>
@@ -12897,10 +12891,10 @@
         <v>0</v>
       </c>
       <c r="W64" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X64" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y64" s="12">
         <v>0</v>
@@ -12963,7 +12957,7 @@
         <v>2</v>
       </c>
       <c r="AS64" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT64" s="1">
         <v>0</v>
@@ -12984,7 +12978,7 @@
         <v>0</v>
       </c>
       <c r="AZ64" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA64" s="10">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="BD64" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE64" s="4">
         <v>43400002</v>
@@ -13016,37 +13010,37 @@
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-      <c r="I65" s="1" t="s">
+      <c r="K65" s="1">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K65" s="1">
-        <v>1</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="M65" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O65" s="1">
         <v>0</v>
@@ -13073,10 +13067,10 @@
         <v>0</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y65" s="1">
         <v>0</v>
@@ -13139,7 +13133,7 @@
         <v>0</v>
       </c>
       <c r="AS65" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT65" s="1">
         <v>0</v>
@@ -13160,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="AZ65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA65" s="1">
         <v>0</v>
@@ -13172,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE65" s="1">
         <v>0</v>
@@ -13192,13 +13186,13 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -13207,7 +13201,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J66" s="1">
         <v>44300001</v>
@@ -13216,13 +13210,13 @@
         <v>1</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O66" s="1">
         <v>0</v>
@@ -13249,10 +13243,10 @@
         <v>0</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y66" s="1">
         <v>0</v>
@@ -13315,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="AS66" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT66" s="1">
         <v>0</v>
@@ -13336,7 +13330,7 @@
         <v>0</v>
       </c>
       <c r="AZ66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA66" s="1">
         <v>0</v>
@@ -13348,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="BD66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE66" s="1">
         <v>0</v>
@@ -13368,13 +13362,13 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -13383,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J67" s="1">
         <v>38500001</v>
@@ -13392,13 +13386,13 @@
         <v>1</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O67" s="1">
         <v>0</v>
@@ -13425,10 +13419,10 @@
         <v>0</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y67" s="1">
         <v>0</v>
@@ -13491,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="AS67" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT67" s="1">
         <v>0</v>
@@ -13512,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="AZ67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA67" s="1">
         <v>0</v>
@@ -13524,7 +13518,7 @@
         <v>0</v>
       </c>
       <c r="BD67" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE67" s="1">
         <v>0</v>
@@ -13544,13 +13538,13 @@
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -13559,7 +13553,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J68" s="1">
         <v>45100001</v>
@@ -13568,13 +13562,13 @@
         <v>1</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O68" s="1">
         <v>0</v>
@@ -13601,10 +13595,10 @@
         <v>0</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y68" s="1">
         <v>0</v>
@@ -13667,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="AS68" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT68" s="1">
         <v>0</v>
@@ -13688,7 +13682,7 @@
         <v>0</v>
       </c>
       <c r="AZ68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA68" s="1">
         <v>0</v>
@@ -13700,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="BD68" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE68" s="1">
         <v>0</v>
@@ -13720,13 +13714,13 @@
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -13735,7 +13729,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J69" s="1">
         <v>44500001</v>
@@ -13744,13 +13738,13 @@
         <v>1</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O69" s="1">
         <v>0</v>
@@ -13777,10 +13771,10 @@
         <v>0</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y69" s="1">
         <v>0</v>
@@ -13843,7 +13837,7 @@
         <v>0</v>
       </c>
       <c r="AS69" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT69" s="1">
         <v>0</v>
@@ -13864,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="AZ69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA69" s="1">
         <v>0</v>
@@ -13876,7 +13870,7 @@
         <v>0</v>
       </c>
       <c r="BD69" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE69" s="1">
         <v>0</v>
@@ -13896,13 +13890,13 @@
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -13911,22 +13905,22 @@
         <v>0</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K70" s="1">
-        <v>1</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="M70" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O70" s="1">
         <v>0</v>
@@ -13953,10 +13947,10 @@
         <v>0</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y70" s="1">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="AS70" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -14040,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="AZ70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA70" s="1">
         <v>0</v>
@@ -14052,7 +14046,7 @@
         <v>0</v>
       </c>
       <c r="BD70" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE70" s="1">
         <v>0</v>
@@ -14072,13 +14066,13 @@
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
@@ -14087,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J71" s="1">
         <v>45600001</v>
@@ -14096,13 +14090,13 @@
         <v>1</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O71" s="1">
         <v>0</v>
@@ -14129,10 +14123,10 @@
         <v>0</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
@@ -14195,7 +14189,7 @@
         <v>0</v>
       </c>
       <c r="AS71" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT71" s="1">
         <v>0</v>
@@ -14216,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA71" s="1">
         <v>0</v>
@@ -14228,7 +14222,7 @@
         <v>0</v>
       </c>
       <c r="BD71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE71" s="1">
         <v>0</v>
@@ -14248,13 +14242,13 @@
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -14263,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="J72" s="1">
         <v>44400001</v>
@@ -14272,13 +14266,13 @@
         <v>1</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O72" s="1">
         <v>0</v>
@@ -14305,10 +14299,10 @@
         <v>0</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X72" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y72" s="1">
         <v>0</v>
@@ -14371,7 +14365,7 @@
         <v>0</v>
       </c>
       <c r="AS72" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT72" s="1">
         <v>0</v>
@@ -14392,7 +14386,7 @@
         <v>0</v>
       </c>
       <c r="AZ72" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA72" s="1">
         <v>0</v>
@@ -14404,7 +14398,7 @@
         <v>0</v>
       </c>
       <c r="BD72" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE72" s="1">
         <v>0</v>
@@ -14424,13 +14418,13 @@
         <v>1</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G73" s="12">
         <v>0</v>
@@ -14439,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J73" s="4">
         <v>48200001</v>
@@ -14448,10 +14442,10 @@
         <v>5</v>
       </c>
       <c r="L73" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M73" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M73" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N73" s="12">
         <v>0</v>
@@ -14481,10 +14475,10 @@
         <v>0</v>
       </c>
       <c r="W73" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X73" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y73" s="12">
         <v>0</v>
@@ -14547,7 +14541,7 @@
         <v>2</v>
       </c>
       <c r="AS73" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT73" s="1">
         <v>0</v>
@@ -14568,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="AZ73" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA73" s="10">
         <v>0</v>
@@ -14580,7 +14574,7 @@
         <v>0</v>
       </c>
       <c r="BD73" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE73" s="4">
         <v>0</v>
@@ -14600,14 +14594,14 @@
         <v>1</v>
       </c>
       <c r="D74" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F74" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="E74" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>168</v>
-      </c>
       <c r="G74" s="12">
         <v>0</v>
       </c>
@@ -14615,7 +14609,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J74" s="4">
         <v>48300001</v>
@@ -14624,10 +14618,10 @@
         <v>5</v>
       </c>
       <c r="L74" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M74" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M74" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N74" s="12">
         <v>0</v>
@@ -14657,10 +14651,10 @@
         <v>0</v>
       </c>
       <c r="W74" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X74" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y74" s="12">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>2</v>
       </c>
       <c r="AS74" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT74" s="1">
         <v>0</v>
@@ -14744,7 +14738,7 @@
         <v>0</v>
       </c>
       <c r="AZ74" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA74" s="10">
         <v>0</v>
@@ -14756,7 +14750,7 @@
         <v>0</v>
       </c>
       <c r="BD74" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE74" s="4">
         <v>0</v>
@@ -14776,13 +14770,13 @@
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G75" s="12">
         <v>0</v>
@@ -14791,7 +14785,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J75" s="4">
         <v>48300002</v>
@@ -14800,10 +14794,10 @@
         <v>5</v>
       </c>
       <c r="L75" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M75" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M75" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N75" s="12">
         <v>0</v>
@@ -14833,10 +14827,10 @@
         <v>0</v>
       </c>
       <c r="W75" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X75" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y75" s="12">
         <v>0</v>
@@ -14899,7 +14893,7 @@
         <v>2</v>
       </c>
       <c r="AS75" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT75" s="1">
         <v>0</v>
@@ -14920,7 +14914,7 @@
         <v>0</v>
       </c>
       <c r="AZ75" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA75" s="10">
         <v>0</v>
@@ -14932,7 +14926,7 @@
         <v>0</v>
       </c>
       <c r="BD75" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE75" s="4">
         <v>0</v>
@@ -14952,13 +14946,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G76" s="12">
         <v>0</v>
@@ -14967,7 +14961,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J76" s="4">
         <v>48300003</v>
@@ -14976,10 +14970,10 @@
         <v>5</v>
       </c>
       <c r="L76" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M76" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M76" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N76" s="12">
         <v>0</v>
@@ -15009,10 +15003,10 @@
         <v>0</v>
       </c>
       <c r="W76" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X76" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y76" s="12">
         <v>0</v>
@@ -15075,7 +15069,7 @@
         <v>2</v>
       </c>
       <c r="AS76" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT76" s="1">
         <v>0</v>
@@ -15096,7 +15090,7 @@
         <v>0</v>
       </c>
       <c r="AZ76" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA76" s="10">
         <v>0</v>
@@ -15108,7 +15102,7 @@
         <v>0</v>
       </c>
       <c r="BD76" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE76" s="4">
         <v>0</v>
@@ -15128,13 +15122,13 @@
         <v>4</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G77" s="12">
         <v>0</v>
@@ -15143,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J77" s="4">
         <v>48300004</v>
@@ -15152,10 +15146,10 @@
         <v>5</v>
       </c>
       <c r="L77" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M77" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M77" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N77" s="12">
         <v>0</v>
@@ -15185,10 +15179,10 @@
         <v>0</v>
       </c>
       <c r="W77" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X77" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y77" s="12">
         <v>0</v>
@@ -15251,7 +15245,7 @@
         <v>2</v>
       </c>
       <c r="AS77" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT77" s="1">
         <v>0</v>
@@ -15272,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="AZ77" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA77" s="10">
         <v>0</v>
@@ -15284,7 +15278,7 @@
         <v>0</v>
       </c>
       <c r="BD77" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE77" s="4">
         <v>0</v>
@@ -15304,22 +15298,22 @@
         <v>5</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12">
+        <v>0</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="G78" s="12">
-        <v>0</v>
-      </c>
-      <c r="H78" s="12">
-        <v>0</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="J78" s="4">
         <v>48300005</v>
@@ -15328,10 +15322,10 @@
         <v>5</v>
       </c>
       <c r="L78" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M78" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M78" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N78" s="12">
         <v>0</v>
@@ -15361,10 +15355,10 @@
         <v>0</v>
       </c>
       <c r="W78" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X78" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y78" s="12">
         <v>0</v>
@@ -15427,7 +15421,7 @@
         <v>2</v>
       </c>
       <c r="AS78" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT78" s="1">
         <v>0</v>
@@ -15448,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="AZ78" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA78" s="10">
         <v>0</v>
@@ -15460,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="BD78" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE78" s="4">
         <v>0</v>
@@ -15480,13 +15474,13 @@
         <v>6</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G79" s="12">
         <v>0</v>
@@ -15495,7 +15489,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J79" s="4">
         <v>48300006</v>
@@ -15504,10 +15498,10 @@
         <v>5</v>
       </c>
       <c r="L79" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M79" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="M79" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="N79" s="12">
         <v>0</v>
@@ -15537,10 +15531,10 @@
         <v>0</v>
       </c>
       <c r="W79" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X79" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y79" s="12">
         <v>0</v>
@@ -15603,7 +15597,7 @@
         <v>2</v>
       </c>
       <c r="AS79" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AT79" s="1">
         <v>0</v>
@@ -15624,7 +15618,7 @@
         <v>0</v>
       </c>
       <c r="AZ79" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA79" s="10">
         <v>0</v>
@@ -15636,7 +15630,7 @@
         <v>0</v>
       </c>
       <c r="BD79" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BE79" s="4">
         <v>0</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_items_v8【迷宫-道具】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18282645-7DC2-4691-A99A-DE806F821AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F044081-6DFA-42BF-92D3-82FA2347DC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" tabRatio="688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -540,7 +538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="198">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1128,7 +1126,27 @@
     <t>技能道具6</t>
   </si>
   <si>
-    <t>items_atlas0</t>
+    <t>items_atlas_0</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限+20%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+20%</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -13938,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U70" s="1">
         <v>0</v>
@@ -14114,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U71" s="1">
         <v>0</v>
@@ -14466,7 +14484,7 @@
         <v>0</v>
       </c>
       <c r="T73" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U73" s="12">
         <v>3</v>
@@ -14642,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U74" s="12">
         <v>3</v>
@@ -14773,7 +14791,7 @@
         <v>187</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>166</v>
@@ -14818,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="T75" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U75" s="12">
         <v>3</v>
@@ -14949,7 +14967,7 @@
         <v>188</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>166</v>
@@ -14994,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U76" s="12">
         <v>3</v>
@@ -15125,7 +15143,7 @@
         <v>189</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>166</v>
@@ -15170,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U77" s="12">
         <v>3</v>
@@ -15301,7 +15319,7 @@
         <v>190</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>166</v>
@@ -15346,7 +15364,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U78" s="12">
         <v>3</v>
@@ -15477,7 +15495,7 @@
         <v>191</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>166</v>
@@ -15522,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U79" s="12">
         <v>3</v>
